--- a/output/Data and Chart Outputs/malaysia_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/malaysia_power_generation_daily.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Demand" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chart - Demand" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Daily" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Demand" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -146,17 +146,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Malaysia (Peninsular) power generation by fuel (GSO) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -177,10 +178,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -205,10 +206,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -233,10 +234,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -261,10 +262,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -289,10 +290,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -317,10 +318,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="008300"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -345,10 +346,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9A9A9A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -381,8 +382,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -408,8 +409,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -426,7 +427,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -440,7 +441,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -449,17 +450,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Malaysia (Peninsular) system demand (GSO) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -479,7 +481,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -489,7 +491,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -515,7 +517,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="EB6834"/>
               </a:solidFill>
@@ -525,7 +527,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -557,8 +559,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -584,8 +586,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -602,7 +604,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -616,7 +618,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -625,7 +627,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>9</col>
@@ -640,9 +642,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -652,7 +654,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -667,9 +669,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1012,7 +1014,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Peninsular Malaysia grid only (Sabah and Sarawak are separate systems). Daily from 2021-01-01 to 2026-10-02.</t>
+          <t>Peninsular Malaysia grid only (Sabah and Sarawak are separate systems). Daily from 2021-01-01 to 2026-10-27.</t>
         </is>
       </c>
     </row>
@@ -1102,16 +1104,16 @@
         <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>937.1674</v>
+        <v>937.1673999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>2961.068</v>
+        <v>2961.068000000001</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>78.9502</v>
+        <v>78.95020000000001</v>
       </c>
       <c r="F2" t="n">
         <v>6277.4879</v>
@@ -1128,7 +1130,7 @@
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>627.4163000000001</v>
+        <v>627.4163</v>
       </c>
       <c r="C3" t="n">
         <v>3313.3692</v>
@@ -1140,13 +1142,13 @@
         <v>96.50410000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>5684.4191</v>
+        <v>5684.419100000001</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>34.64470000000001</v>
+        <v>34.6447</v>
       </c>
     </row>
     <row r="4">
@@ -1166,7 +1168,7 @@
         <v>102.5258</v>
       </c>
       <c r="F4" t="n">
-        <v>7161.4488</v>
+        <v>7161.448800000001</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1189,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>93.74260000000001</v>
+        <v>93.74260000000002</v>
       </c>
       <c r="F5" t="n">
         <v>6425.1052</v>
@@ -1209,7 +1211,7 @@
         <v>543.5706</v>
       </c>
       <c r="C6" t="n">
-        <v>3863.3511</v>
+        <v>3863.351100000001</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1218,7 +1220,7 @@
         <v>95.71560000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>6467.8818</v>
+        <v>6467.881800000001</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1244,7 +1246,7 @@
         <v>94.35419999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>5311.4863</v>
+        <v>5311.486299999999</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1319,10 +1321,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>94.9914</v>
+        <v>94.99140000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>6495.9393</v>
+        <v>6495.939299999999</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1339,7 +1341,7 @@
         <v>650.7763</v>
       </c>
       <c r="C11" t="n">
-        <v>3572.4923</v>
+        <v>3572.492299999999</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1362,19 +1364,19 @@
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>603.0373000000001</v>
+        <v>603.0373</v>
       </c>
       <c r="C12" t="n">
-        <v>4123.0695</v>
+        <v>4123.069500000001</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>80.17449999999999</v>
+        <v>80.17449999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>5734.463</v>
+        <v>5734.463000000001</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1400,7 +1402,7 @@
         <v>81.82210000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>6106.9089</v>
+        <v>6106.908900000001</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1414,10 +1416,10 @@
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>649.7595</v>
+        <v>649.7595000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>4360.418900000001</v>
+        <v>4360.4189</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1426,7 +1428,7 @@
         <v>97.09869999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>5539.2463</v>
+        <v>5539.246300000001</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1469,7 +1471,7 @@
         <v>458.0033</v>
       </c>
       <c r="C16" t="n">
-        <v>4078.3979</v>
+        <v>4078.397899999999</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1510,7 +1512,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>46.35619999999999</v>
+        <v>46.3562</v>
       </c>
     </row>
     <row r="18">
@@ -1547,7 +1549,7 @@
         <v>398.7805</v>
       </c>
       <c r="C19" t="n">
-        <v>4219.7</v>
+        <v>4219.700000000001</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1556,7 +1558,7 @@
         <v>134.917</v>
       </c>
       <c r="F19" t="n">
-        <v>6217.2387</v>
+        <v>6217.238699999999</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1582,7 +1584,7 @@
         <v>151.7994</v>
       </c>
       <c r="F20" t="n">
-        <v>6645.1415</v>
+        <v>6645.141499999999</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1596,7 +1598,7 @@
         <v>44774</v>
       </c>
       <c r="B21" t="n">
-        <v>725.7003000000001</v>
+        <v>725.7003</v>
       </c>
       <c r="C21" t="n">
         <v>4016.4168</v>
@@ -1622,10 +1624,10 @@
         <v>44805</v>
       </c>
       <c r="B22" t="n">
-        <v>671.8083</v>
+        <v>671.8083000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>4240.4623</v>
+        <v>4240.462300000001</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1648,7 +1650,7 @@
         <v>44835</v>
       </c>
       <c r="B23" t="n">
-        <v>715.6264</v>
+        <v>715.6264000000001</v>
       </c>
       <c r="C23" t="n">
         <v>3467.9889</v>
@@ -1674,10 +1676,10 @@
         <v>44866</v>
       </c>
       <c r="B24" t="n">
-        <v>596.1345</v>
+        <v>596.1344999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>4356.183400000001</v>
+        <v>4356.1834</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1729,7 +1731,7 @@
         <v>580.8121</v>
       </c>
       <c r="C26" t="n">
-        <v>4274.860900000001</v>
+        <v>4274.8609</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1738,7 +1740,7 @@
         <v>145.7333</v>
       </c>
       <c r="F26" t="n">
-        <v>5467.0324</v>
+        <v>5467.032399999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1752,7 +1754,7 @@
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>593.215</v>
+        <v>593.2149999999999</v>
       </c>
       <c r="C27" t="n">
         <v>3697.2844</v>
@@ -1781,7 +1783,7 @@
         <v>423.53</v>
       </c>
       <c r="C28" t="n">
-        <v>4554.2478</v>
+        <v>4554.247800000001</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1804,10 +1806,10 @@
         <v>45017</v>
       </c>
       <c r="B29" t="n">
-        <v>394.0265</v>
+        <v>394.0264999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>3850.8392</v>
+        <v>3850.839199999999</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1842,7 +1844,7 @@
         <v>192.9999</v>
       </c>
       <c r="F30" t="n">
-        <v>7345.942400000001</v>
+        <v>7345.942399999998</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1859,7 +1861,7 @@
         <v>426.3052</v>
       </c>
       <c r="C31" t="n">
-        <v>3948.4851</v>
+        <v>3948.485099999999</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1882,10 +1884,10 @@
         <v>45108</v>
       </c>
       <c r="B32" t="n">
-        <v>469.3589</v>
+        <v>469.3589000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>4091.7199</v>
+        <v>4091.719900000001</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1894,7 +1896,7 @@
         <v>179.2128</v>
       </c>
       <c r="F32" t="n">
-        <v>6761.2883</v>
+        <v>6761.288300000001</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1946,7 +1948,7 @@
         <v>175.8141</v>
       </c>
       <c r="F34" t="n">
-        <v>6330.1531</v>
+        <v>6330.153100000001</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1986,7 +1988,7 @@
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>477.8107</v>
+        <v>477.8106999999999</v>
       </c>
       <c r="C36" t="n">
         <v>4307.0878</v>
@@ -1998,7 +2000,7 @@
         <v>149.052</v>
       </c>
       <c r="F36" t="n">
-        <v>6077.501</v>
+        <v>6077.501000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2012,7 +2014,7 @@
         <v>45261</v>
       </c>
       <c r="B37" t="n">
-        <v>618.0975</v>
+        <v>618.0975000000001</v>
       </c>
       <c r="C37" t="n">
         <v>4044.5979</v>
@@ -2064,7 +2066,7 @@
         <v>45323</v>
       </c>
       <c r="B39" t="n">
-        <v>667.1574000000001</v>
+        <v>667.1573999999999</v>
       </c>
       <c r="C39" t="n">
         <v>4628.2795</v>
@@ -2076,7 +2078,7 @@
         <v>241.125</v>
       </c>
       <c r="F39" t="n">
-        <v>5456.7963</v>
+        <v>5456.796300000001</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2090,7 +2092,7 @@
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>557.4556</v>
+        <v>557.4556000000001</v>
       </c>
       <c r="C40" t="n">
         <v>4778.3108</v>
@@ -2108,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>35.094</v>
+        <v>35.09400000000001</v>
       </c>
     </row>
     <row r="41">
@@ -2128,7 +2130,7 @@
         <v>258.3095</v>
       </c>
       <c r="F41" t="n">
-        <v>6537.9743</v>
+        <v>6537.974300000001</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2229,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>274.8252</v>
+        <v>274.8252000000001</v>
       </c>
       <c r="F45" t="n">
         <v>7059.8297</v>
@@ -2249,7 +2251,7 @@
         <v>361.6703</v>
       </c>
       <c r="C46" t="n">
-        <v>3876.8785</v>
+        <v>3876.878499999999</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2275,7 +2277,7 @@
         <v>580.1574000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>4517.0912</v>
+        <v>4517.091199999999</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2298,10 +2300,10 @@
         <v>45597</v>
       </c>
       <c r="B48" t="n">
-        <v>671.8748000000001</v>
+        <v>671.8748000000002</v>
       </c>
       <c r="C48" t="n">
-        <v>3734.0846</v>
+        <v>3734.084599999999</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2310,7 +2312,7 @@
         <v>224.4243</v>
       </c>
       <c r="F48" t="n">
-        <v>6868.835</v>
+        <v>6868.834999999999</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -2336,7 +2338,7 @@
         <v>227.8284</v>
       </c>
       <c r="F49" t="n">
-        <v>6941.8003</v>
+        <v>6941.800300000001</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2353,7 +2355,7 @@
         <v>809.4713</v>
       </c>
       <c r="C50" t="n">
-        <v>3900.0542</v>
+        <v>3900.054199999999</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2362,7 +2364,7 @@
         <v>249.999</v>
       </c>
       <c r="F50" t="n">
-        <v>6371.8827</v>
+        <v>6371.882700000001</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2379,7 +2381,7 @@
         <v>510.1767</v>
       </c>
       <c r="C51" t="n">
-        <v>3928.5316</v>
+        <v>3928.531600000001</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2388,7 +2390,7 @@
         <v>277.1269</v>
       </c>
       <c r="F51" t="n">
-        <v>5932.2577</v>
+        <v>5932.257699999999</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2402,7 +2404,7 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>456.5983</v>
+        <v>456.5983000000001</v>
       </c>
       <c r="C52" t="n">
         <v>3903.2825</v>
@@ -2411,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>311.1525</v>
+        <v>311.1524999999999</v>
       </c>
       <c r="F52" t="n">
         <v>7398.6176</v>
@@ -2437,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>299.0256</v>
+        <v>299.0256000000001</v>
       </c>
       <c r="F53" t="n">
         <v>7258.7967</v>
@@ -2454,7 +2456,7 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>595.7814000000001</v>
+        <v>595.7814000000002</v>
       </c>
       <c r="C54" t="n">
         <v>4291.7598</v>
@@ -2466,7 +2468,7 @@
         <v>294.7454</v>
       </c>
       <c r="F54" t="n">
-        <v>7470.8483</v>
+        <v>7470.848299999999</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2483,22 +2485,22 @@
         <v>511.4286</v>
       </c>
       <c r="C55" t="n">
-        <v>3576.5718</v>
+        <v>3576.571799999999</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>275.5743</v>
+        <v>275.5743000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>7708.9221</v>
+        <v>7708.922100000001</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>73.5048</v>
+        <v>73.50479999999999</v>
       </c>
     </row>
     <row r="56">
@@ -2506,7 +2508,7 @@
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>697.1299</v>
+        <v>697.1298999999999</v>
       </c>
       <c r="C56" t="n">
         <v>4154.6309</v>
@@ -2518,7 +2520,7 @@
         <v>306.2035</v>
       </c>
       <c r="F56" t="n">
-        <v>7579.7292</v>
+        <v>7579.729199999999</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2558,10 +2560,10 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>577.3247</v>
+        <v>577.3247000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>4164.3463</v>
+        <v>4164.346299999999</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2570,7 +2572,7 @@
         <v>288.2524</v>
       </c>
       <c r="F58" t="n">
-        <v>6717.9182</v>
+        <v>6717.918199999999</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2596,7 +2598,7 @@
         <v>290.8767</v>
       </c>
       <c r="F59" t="n">
-        <v>7051.0003</v>
+        <v>7051.000300000001</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2610,7 +2612,7 @@
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>658.3330999999999</v>
+        <v>658.3331000000001</v>
       </c>
       <c r="C60" t="n">
         <v>3808.0333</v>
@@ -2639,13 +2641,13 @@
         <v>620.2604</v>
       </c>
       <c r="C61" t="n">
-        <v>4572.4396</v>
+        <v>4572.439600000001</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>264.0892</v>
+        <v>264.0891999999999</v>
       </c>
       <c r="F61" t="n">
         <v>6641.072700000001</v>
@@ -2662,7 +2664,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>367.9545</v>
+        <v>367.9544999999999</v>
       </c>
       <c r="C62" t="n">
         <v>4892.297</v>
@@ -2697,16 +2699,16 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>281.4196</v>
+        <v>281.4196000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>6040.8054</v>
+        <v>6040.805399999999</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>81.25689999999999</v>
+        <v>81.2569</v>
       </c>
     </row>
     <row r="64">
@@ -2717,7 +2719,7 @@
         <v>313.9901</v>
       </c>
       <c r="C64" t="n">
-        <v>4669.0419</v>
+        <v>4669.041899999999</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -2743,16 +2745,16 @@
         <v>302.9702</v>
       </c>
       <c r="C65" t="n">
-        <v>5551.6446</v>
+        <v>5551.644600000001</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>339.7921</v>
+        <v>339.7921000000001</v>
       </c>
       <c r="F65" t="n">
-        <v>6662.607</v>
+        <v>6662.606999999999</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2769,7 +2771,7 @@
         <v>321.4642</v>
       </c>
       <c r="C66" t="n">
-        <v>5490.4266</v>
+        <v>5490.426600000001</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -2804,7 +2806,7 @@
         <v>302.2544</v>
       </c>
       <c r="F67" t="n">
-        <v>6976.675099999999</v>
+        <v>6976.6751</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2827,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>313.8714000000001</v>
+        <v>313.8713999999999</v>
       </c>
       <c r="F68" t="n">
         <v>7502.9403</v>
@@ -2896,25 +2898,25 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>21.2004</v>
+        <v>338.4881999999999</v>
       </c>
       <c r="C71" t="n">
-        <v>320.5629</v>
+        <v>4508.7772</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>23.2027</v>
+        <v>280.3343</v>
       </c>
       <c r="F71" t="n">
-        <v>513.9611</v>
+        <v>6536.736999999999</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>224.474</v>
       </c>
     </row>
   </sheetData>
@@ -3716,10 +3718,10 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>18327.5</v>
+        <v>18335.55555555555</v>
       </c>
       <c r="C71" t="n">
-        <v>20709</v>
+        <v>20869.14814814815</v>
       </c>
     </row>
   </sheetData>
@@ -3734,7 +3736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2102"/>
+  <dimension ref="A1:I2127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64710,6 +64712,731 @@
         <v>441688.7</v>
       </c>
       <c r="I2102" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>8998</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>148880.8</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>12088.2</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>250814.5</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2103" t="n">
+        <v>420781.5</v>
+      </c>
+      <c r="I2103" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>11464.2</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>132374.3</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>12225.8</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>245985.5</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2104" t="n">
+        <v>402049.8</v>
+      </c>
+      <c r="I2104" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>10547.8</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>160138</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>12140.2</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>259125.8</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>6252.2</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2105" t="n">
+        <v>448204</v>
+      </c>
+      <c r="I2105" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>11674.2</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>168352.7</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>9702.799999999999</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>259606.8</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>9984.700000000001</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2106" t="n">
+        <v>459321.2</v>
+      </c>
+      <c r="I2106" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>15566.2</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>169541.5</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>10174.7</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>250506.3</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>13445.3</v>
+      </c>
+      <c r="G2107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2107" t="n">
+        <v>459234</v>
+      </c>
+      <c r="I2107" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>13763.3</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>172963.5</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>10812.8</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>241654</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>18315.3</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2108" t="n">
+        <v>457509</v>
+      </c>
+      <c r="I2108" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>13499.8</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>176331.7</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>10308.3</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>240879.8</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>16414.3</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2109" t="n">
+        <v>457434</v>
+      </c>
+      <c r="I2109" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>13423.5</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>164416.8</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>9490.200000000001</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>233738.8</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>12348.5</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2110" t="n">
+        <v>433417.8</v>
+      </c>
+      <c r="I2110" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>11225.2</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>156778.5</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>11001.7</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>217066.2</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>10700.3</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2111" t="n">
+        <v>406771.8</v>
+      </c>
+      <c r="I2111" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>13767.2</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>177670.2</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>7351</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>227063</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>16594.3</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2112" t="n">
+        <v>442445.7</v>
+      </c>
+      <c r="I2112" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>11876.8</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>160946.7</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>12302.5</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>250525.5</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>10528.5</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2113" t="n">
+        <v>446180</v>
+      </c>
+      <c r="I2113" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>15434.3</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>170426.2</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>11526.3</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>249512.7</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>11006.8</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2114" t="n">
+        <v>457906.3</v>
+      </c>
+      <c r="I2114" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>12625.5</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>184115.2</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>11004.5</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>239334.5</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>13086.7</v>
+      </c>
+      <c r="G2115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2115" t="n">
+        <v>460166.3</v>
+      </c>
+      <c r="I2115" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>16533.2</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>160553.7</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>11256.2</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>240757.2</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>22274</v>
+      </c>
+      <c r="G2116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2116" t="n">
+        <v>451374.2</v>
+      </c>
+      <c r="I2116" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>11825.2</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>155342.7</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>9772.799999999999</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>239734.7</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>11940.3</v>
+      </c>
+      <c r="G2117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2117" t="n">
+        <v>428615.7</v>
+      </c>
+      <c r="I2117" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>11702.8</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>155513</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>7671.5</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>223185.7</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>4317.8</v>
+      </c>
+      <c r="G2118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2118" t="n">
+        <v>402390.8</v>
+      </c>
+      <c r="I2118" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>15726.2</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>186086.8</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>10515.2</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>228548</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>4120.3</v>
+      </c>
+      <c r="G2119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2119" t="n">
+        <v>444996.5</v>
+      </c>
+      <c r="I2119" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2120" t="n">
+        <v>14102.5</v>
+      </c>
+      <c r="C2120" t="n">
+        <v>198890.3</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>10348</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>232027.7</v>
+      </c>
+      <c r="F2120" t="n">
+        <v>5396</v>
+      </c>
+      <c r="G2120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2120" t="n">
+        <v>460764.5</v>
+      </c>
+      <c r="I2120" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2121" t="n">
+        <v>14572.5</v>
+      </c>
+      <c r="C2121" t="n">
+        <v>184738.7</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>10905.2</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>235915.2</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>9731.700000000001</v>
+      </c>
+      <c r="G2121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2121" t="n">
+        <v>455863.2</v>
+      </c>
+      <c r="I2121" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>15780.7</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>186502.7</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>12615.8</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>230022</v>
+      </c>
+      <c r="F2122" t="n">
+        <v>14576.7</v>
+      </c>
+      <c r="G2122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2122" t="n">
+        <v>459497.8</v>
+      </c>
+      <c r="I2122" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2123" t="n">
+        <v>12414.3</v>
+      </c>
+      <c r="C2123" t="n">
+        <v>198767</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>10182.2</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>222054.3</v>
+      </c>
+      <c r="F2123" t="n">
+        <v>12766.8</v>
+      </c>
+      <c r="G2123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2123" t="n">
+        <v>456184.7</v>
+      </c>
+      <c r="I2123" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2124" t="n">
+        <v>10870.3</v>
+      </c>
+      <c r="C2124" t="n">
+        <v>176895.3</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>8841.5</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>232121.2</v>
+      </c>
+      <c r="F2124" t="n">
+        <v>673.5</v>
+      </c>
+      <c r="G2124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2124" t="n">
+        <v>429401.8</v>
+      </c>
+      <c r="I2124" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2125" t="n">
+        <v>8962.299999999999</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>134550.2</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>7060.7</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>247471.7</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2125" t="n">
+        <v>398044.8</v>
+      </c>
+      <c r="I2125" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2126" t="n">
+        <v>11863.8</v>
+      </c>
+      <c r="C2126" t="n">
+        <v>146765.5</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>9050.5</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>258301.5</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2126" t="n">
+        <v>425981.3</v>
+      </c>
+      <c r="I2126" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B2127" t="n">
+        <v>9068</v>
+      </c>
+      <c r="C2127" t="n">
+        <v>160672.3</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>8783</v>
+      </c>
+      <c r="E2127" t="n">
+        <v>266823.3</v>
+      </c>
+      <c r="F2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2127" t="n">
+        <v>445346.7</v>
+      </c>
+      <c r="I2127" t="n">
         <v>144</v>
       </c>
     </row>
@@ -64724,7 +65451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2102"/>
+  <dimension ref="A1:D2127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94163,6 +94890,356 @@
         <v>16061</v>
       </c>
     </row>
+    <row r="2103">
+      <c r="A2103" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>17557</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>20273</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>15235</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>16386</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>19723</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>14540</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>18671</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>21509</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>15588</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>19141</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>21730</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>16529</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>19169</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>21591</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>16599</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>19108</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>21503</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>16571</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>19095</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>21495</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>16617</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>18080</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>20166</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>15890</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>16973</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>19800</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>14632</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>18459</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>20568</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>15549</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>18627</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>21343</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>15776</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>19093</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>21855</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>16308</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>19187</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>21691</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>16594</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>18822</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>20994</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>16479</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>17872</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>19972</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>15590</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>16801</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>19535</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>14801</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>18184</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>21873</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>15309</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2120" t="n">
+        <v>19220</v>
+      </c>
+      <c r="C2120" t="n">
+        <v>21481</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>16723</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2121" t="n">
+        <v>19024</v>
+      </c>
+      <c r="C2121" t="n">
+        <v>21591</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>16328</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>19166</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>21833</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>16483</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2123" t="n">
+        <v>19027</v>
+      </c>
+      <c r="C2123" t="n">
+        <v>20955</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>16774</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2124" t="n">
+        <v>17910</v>
+      </c>
+      <c r="C2124" t="n">
+        <v>20306</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>15828</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2125" t="n">
+        <v>16576</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>18892</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>14760</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2126" t="n">
+        <v>17732</v>
+      </c>
+      <c r="C2126" t="n">
+        <v>20754</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>14911</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B2127" t="n">
+        <v>18525</v>
+      </c>
+      <c r="C2127" t="n">
+        <v>20616</v>
+      </c>
+      <c r="D2127" t="n">
+        <v>15865</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/malaysia_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/malaysia_power_generation_daily.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -158,7 +159,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Malaysia (Peninsular) power generation by fuel (GSO) (to Oct/26)</a:t>
+              <a:t>Malaysia (Peninsular) power generation by fuel (GSO) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -188,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$71</f>
+              <f>'Chart'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -216,12 +217,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$71</f>
+              <f>'Chart'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -244,12 +245,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$71</f>
+              <f>'Chart'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -272,12 +273,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$71</f>
+              <f>'Chart'!$E$2:$E$70</f>
             </numRef>
           </val>
         </ser>
@@ -300,12 +301,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$71</f>
+              <f>'Chart'!$F$2:$F$70</f>
             </numRef>
           </val>
         </ser>
@@ -328,12 +329,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$71</f>
+              <f>'Chart'!$G$2:$G$70</f>
             </numRef>
           </val>
         </ser>
@@ -356,12 +357,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$71</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$71</f>
+              <f>'Chart'!$H$2:$H$70</f>
             </numRef>
           </val>
         </ser>
@@ -1003,7 +1004,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Peninsular Malaysia grid only (Sabah and Sarawak are separate systems). Daily from 2021-01-01 to 2026-10-27.</t>
+          <t>Peninsular Malaysia grid only (Sabah and Sarawak are separate systems). Daily from 2021-01-01 to 2026-10-02.</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -1051,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1100,7 +1099,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1126,7 +1125,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1152,7 +1151,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1178,7 +1177,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1204,7 +1203,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1230,7 +1229,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1256,7 +1255,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1282,7 +1281,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1308,7 +1307,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1334,7 +1333,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1360,7 +1359,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1386,7 +1385,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1412,7 +1411,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1438,7 +1437,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1464,7 +1463,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1490,7 +1489,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1516,7 +1515,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1542,7 +1541,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1568,7 +1567,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1594,7 +1593,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1620,7 +1619,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1646,7 +1645,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1672,7 +1671,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1698,7 +1697,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1724,7 +1723,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1750,7 +1749,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1776,7 +1775,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1802,7 +1801,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1828,7 +1827,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1854,7 +1853,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1880,7 +1879,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1906,7 +1905,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1932,7 +1931,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1958,7 +1957,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1984,7 +1983,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -2010,7 +2009,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2036,7 +2035,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2062,7 +2061,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2088,7 +2087,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2114,7 +2113,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2140,7 +2139,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2166,7 +2165,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2192,7 +2191,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2218,7 +2217,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2244,7 +2243,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2270,7 +2269,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2296,7 +2295,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2322,7 +2321,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2348,7 +2347,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2374,7 +2373,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2400,7 +2399,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2426,7 +2425,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2452,7 +2451,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2478,7 +2477,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2504,7 +2503,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2530,7 +2529,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2556,7 +2555,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2582,7 +2581,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2608,7 +2607,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2634,7 +2633,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2660,7 +2659,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2686,7 +2685,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2712,7 +2711,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2738,7 +2737,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2764,7 +2763,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2790,7 +2789,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2816,7 +2815,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2842,7 +2841,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2868,7 +2867,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
@@ -2891,32 +2890,6 @@
       </c>
       <c r="H70" t="n">
         <v>91.72019999999999</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B71" t="n">
-        <v>338.4881999999999</v>
-      </c>
-      <c r="C71" t="n">
-        <v>4508.7772</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>280.3343</v>
-      </c>
-      <c r="F71" t="n">
-        <v>6536.736999999999</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>224.474</v>
       </c>
     </row>
   </sheetData>
@@ -2955,7 +2928,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -2966,7 +2939,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -2977,7 +2950,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -2988,7 +2961,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -2999,7 +2972,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -3010,7 +2983,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -3021,7 +2994,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -3032,7 +3005,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -3043,7 +3016,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -3054,7 +3027,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -3065,7 +3038,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -3076,7 +3049,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -3087,7 +3060,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -3098,7 +3071,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -3109,7 +3082,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -3120,7 +3093,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -3131,7 +3104,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -3142,7 +3115,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -3153,7 +3126,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -3164,7 +3137,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -3175,7 +3148,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -3186,7 +3159,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -3197,7 +3170,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -3208,7 +3181,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -3219,7 +3192,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -3230,7 +3203,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -3241,7 +3214,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -3252,7 +3225,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -3263,7 +3236,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -3274,7 +3247,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -3285,7 +3258,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -3296,7 +3269,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -3307,7 +3280,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -3318,7 +3291,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -3329,7 +3302,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -3340,7 +3313,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -3351,7 +3324,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -3362,7 +3335,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -3373,7 +3346,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -3384,7 +3357,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -3395,7 +3368,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -3406,7 +3379,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -3417,7 +3390,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -3428,7 +3401,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -3439,7 +3412,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -3450,7 +3423,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -3461,7 +3434,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -3472,7 +3445,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -3483,7 +3456,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -3494,7 +3467,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -3505,7 +3478,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -3516,7 +3489,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -3527,7 +3500,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -3538,7 +3511,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -3549,7 +3522,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -3560,7 +3533,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -3571,7 +3544,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -3582,7 +3555,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -3593,7 +3566,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -3604,7 +3577,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -3615,7 +3588,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -3626,7 +3599,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -3637,7 +3610,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -3648,7 +3621,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -3659,7 +3632,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -3670,7 +3643,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -3681,7 +3654,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -3692,7 +3665,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -3703,7 +3676,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
@@ -3714,14 +3687,14 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>18335.55555555555</v>
+        <v>18327.5</v>
       </c>
       <c r="C71" t="n">
-        <v>20869.14814814815</v>
+        <v>20709</v>
       </c>
     </row>
   </sheetData>
@@ -3736,7 +3709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2127"/>
+  <dimension ref="A1:I2102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64712,731 +64685,6 @@
         <v>441688.7</v>
       </c>
       <c r="I2102" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2103">
-      <c r="A2103" s="4" t="n">
-        <v>46298</v>
-      </c>
-      <c r="B2103" t="n">
-        <v>8998</v>
-      </c>
-      <c r="C2103" t="n">
-        <v>148880.8</v>
-      </c>
-      <c r="D2103" t="n">
-        <v>12088.2</v>
-      </c>
-      <c r="E2103" t="n">
-        <v>250814.5</v>
-      </c>
-      <c r="F2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2103" t="n">
-        <v>420781.5</v>
-      </c>
-      <c r="I2103" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" s="4" t="n">
-        <v>46299</v>
-      </c>
-      <c r="B2104" t="n">
-        <v>11464.2</v>
-      </c>
-      <c r="C2104" t="n">
-        <v>132374.3</v>
-      </c>
-      <c r="D2104" t="n">
-        <v>12225.8</v>
-      </c>
-      <c r="E2104" t="n">
-        <v>245985.5</v>
-      </c>
-      <c r="F2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2104" t="n">
-        <v>402049.8</v>
-      </c>
-      <c r="I2104" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" s="4" t="n">
-        <v>46300</v>
-      </c>
-      <c r="B2105" t="n">
-        <v>10547.8</v>
-      </c>
-      <c r="C2105" t="n">
-        <v>160138</v>
-      </c>
-      <c r="D2105" t="n">
-        <v>12140.2</v>
-      </c>
-      <c r="E2105" t="n">
-        <v>259125.8</v>
-      </c>
-      <c r="F2105" t="n">
-        <v>6252.2</v>
-      </c>
-      <c r="G2105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2105" t="n">
-        <v>448204</v>
-      </c>
-      <c r="I2105" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" s="4" t="n">
-        <v>46301</v>
-      </c>
-      <c r="B2106" t="n">
-        <v>11674.2</v>
-      </c>
-      <c r="C2106" t="n">
-        <v>168352.7</v>
-      </c>
-      <c r="D2106" t="n">
-        <v>9702.799999999999</v>
-      </c>
-      <c r="E2106" t="n">
-        <v>259606.8</v>
-      </c>
-      <c r="F2106" t="n">
-        <v>9984.700000000001</v>
-      </c>
-      <c r="G2106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2106" t="n">
-        <v>459321.2</v>
-      </c>
-      <c r="I2106" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" s="4" t="n">
-        <v>46302</v>
-      </c>
-      <c r="B2107" t="n">
-        <v>15566.2</v>
-      </c>
-      <c r="C2107" t="n">
-        <v>169541.5</v>
-      </c>
-      <c r="D2107" t="n">
-        <v>10174.7</v>
-      </c>
-      <c r="E2107" t="n">
-        <v>250506.3</v>
-      </c>
-      <c r="F2107" t="n">
-        <v>13445.3</v>
-      </c>
-      <c r="G2107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2107" t="n">
-        <v>459234</v>
-      </c>
-      <c r="I2107" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" s="4" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B2108" t="n">
-        <v>13763.3</v>
-      </c>
-      <c r="C2108" t="n">
-        <v>172963.5</v>
-      </c>
-      <c r="D2108" t="n">
-        <v>10812.8</v>
-      </c>
-      <c r="E2108" t="n">
-        <v>241654</v>
-      </c>
-      <c r="F2108" t="n">
-        <v>18315.3</v>
-      </c>
-      <c r="G2108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2108" t="n">
-        <v>457509</v>
-      </c>
-      <c r="I2108" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" s="4" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B2109" t="n">
-        <v>13499.8</v>
-      </c>
-      <c r="C2109" t="n">
-        <v>176331.7</v>
-      </c>
-      <c r="D2109" t="n">
-        <v>10308.3</v>
-      </c>
-      <c r="E2109" t="n">
-        <v>240879.8</v>
-      </c>
-      <c r="F2109" t="n">
-        <v>16414.3</v>
-      </c>
-      <c r="G2109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2109" t="n">
-        <v>457434</v>
-      </c>
-      <c r="I2109" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" s="4" t="n">
-        <v>46305</v>
-      </c>
-      <c r="B2110" t="n">
-        <v>13423.5</v>
-      </c>
-      <c r="C2110" t="n">
-        <v>164416.8</v>
-      </c>
-      <c r="D2110" t="n">
-        <v>9490.200000000001</v>
-      </c>
-      <c r="E2110" t="n">
-        <v>233738.8</v>
-      </c>
-      <c r="F2110" t="n">
-        <v>12348.5</v>
-      </c>
-      <c r="G2110" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2110" t="n">
-        <v>433417.8</v>
-      </c>
-      <c r="I2110" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" s="4" t="n">
-        <v>46306</v>
-      </c>
-      <c r="B2111" t="n">
-        <v>11225.2</v>
-      </c>
-      <c r="C2111" t="n">
-        <v>156778.5</v>
-      </c>
-      <c r="D2111" t="n">
-        <v>11001.7</v>
-      </c>
-      <c r="E2111" t="n">
-        <v>217066.2</v>
-      </c>
-      <c r="F2111" t="n">
-        <v>10700.3</v>
-      </c>
-      <c r="G2111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2111" t="n">
-        <v>406771.8</v>
-      </c>
-      <c r="I2111" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" s="4" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B2112" t="n">
-        <v>13767.2</v>
-      </c>
-      <c r="C2112" t="n">
-        <v>177670.2</v>
-      </c>
-      <c r="D2112" t="n">
-        <v>7351</v>
-      </c>
-      <c r="E2112" t="n">
-        <v>227063</v>
-      </c>
-      <c r="F2112" t="n">
-        <v>16594.3</v>
-      </c>
-      <c r="G2112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2112" t="n">
-        <v>442445.7</v>
-      </c>
-      <c r="I2112" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" s="4" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B2113" t="n">
-        <v>11876.8</v>
-      </c>
-      <c r="C2113" t="n">
-        <v>160946.7</v>
-      </c>
-      <c r="D2113" t="n">
-        <v>12302.5</v>
-      </c>
-      <c r="E2113" t="n">
-        <v>250525.5</v>
-      </c>
-      <c r="F2113" t="n">
-        <v>10528.5</v>
-      </c>
-      <c r="G2113" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2113" t="n">
-        <v>446180</v>
-      </c>
-      <c r="I2113" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" s="4" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B2114" t="n">
-        <v>15434.3</v>
-      </c>
-      <c r="C2114" t="n">
-        <v>170426.2</v>
-      </c>
-      <c r="D2114" t="n">
-        <v>11526.3</v>
-      </c>
-      <c r="E2114" t="n">
-        <v>249512.7</v>
-      </c>
-      <c r="F2114" t="n">
-        <v>11006.8</v>
-      </c>
-      <c r="G2114" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2114" t="n">
-        <v>457906.3</v>
-      </c>
-      <c r="I2114" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B2115" t="n">
-        <v>12625.5</v>
-      </c>
-      <c r="C2115" t="n">
-        <v>184115.2</v>
-      </c>
-      <c r="D2115" t="n">
-        <v>11004.5</v>
-      </c>
-      <c r="E2115" t="n">
-        <v>239334.5</v>
-      </c>
-      <c r="F2115" t="n">
-        <v>13086.7</v>
-      </c>
-      <c r="G2115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2115" t="n">
-        <v>460166.3</v>
-      </c>
-      <c r="I2115" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B2116" t="n">
-        <v>16533.2</v>
-      </c>
-      <c r="C2116" t="n">
-        <v>160553.7</v>
-      </c>
-      <c r="D2116" t="n">
-        <v>11256.2</v>
-      </c>
-      <c r="E2116" t="n">
-        <v>240757.2</v>
-      </c>
-      <c r="F2116" t="n">
-        <v>22274</v>
-      </c>
-      <c r="G2116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2116" t="n">
-        <v>451374.2</v>
-      </c>
-      <c r="I2116" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B2117" t="n">
-        <v>11825.2</v>
-      </c>
-      <c r="C2117" t="n">
-        <v>155342.7</v>
-      </c>
-      <c r="D2117" t="n">
-        <v>9772.799999999999</v>
-      </c>
-      <c r="E2117" t="n">
-        <v>239734.7</v>
-      </c>
-      <c r="F2117" t="n">
-        <v>11940.3</v>
-      </c>
-      <c r="G2117" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2117" t="n">
-        <v>428615.7</v>
-      </c>
-      <c r="I2117" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="B2118" t="n">
-        <v>11702.8</v>
-      </c>
-      <c r="C2118" t="n">
-        <v>155513</v>
-      </c>
-      <c r="D2118" t="n">
-        <v>7671.5</v>
-      </c>
-      <c r="E2118" t="n">
-        <v>223185.7</v>
-      </c>
-      <c r="F2118" t="n">
-        <v>4317.8</v>
-      </c>
-      <c r="G2118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2118" t="n">
-        <v>402390.8</v>
-      </c>
-      <c r="I2118" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" s="4" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B2119" t="n">
-        <v>15726.2</v>
-      </c>
-      <c r="C2119" t="n">
-        <v>186086.8</v>
-      </c>
-      <c r="D2119" t="n">
-        <v>10515.2</v>
-      </c>
-      <c r="E2119" t="n">
-        <v>228548</v>
-      </c>
-      <c r="F2119" t="n">
-        <v>4120.3</v>
-      </c>
-      <c r="G2119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2119" t="n">
-        <v>444996.5</v>
-      </c>
-      <c r="I2119" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" s="4" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B2120" t="n">
-        <v>14102.5</v>
-      </c>
-      <c r="C2120" t="n">
-        <v>198890.3</v>
-      </c>
-      <c r="D2120" t="n">
-        <v>10348</v>
-      </c>
-      <c r="E2120" t="n">
-        <v>232027.7</v>
-      </c>
-      <c r="F2120" t="n">
-        <v>5396</v>
-      </c>
-      <c r="G2120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2120" t="n">
-        <v>460764.5</v>
-      </c>
-      <c r="I2120" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" s="4" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B2121" t="n">
-        <v>14572.5</v>
-      </c>
-      <c r="C2121" t="n">
-        <v>184738.7</v>
-      </c>
-      <c r="D2121" t="n">
-        <v>10905.2</v>
-      </c>
-      <c r="E2121" t="n">
-        <v>235915.2</v>
-      </c>
-      <c r="F2121" t="n">
-        <v>9731.700000000001</v>
-      </c>
-      <c r="G2121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2121" t="n">
-        <v>455863.2</v>
-      </c>
-      <c r="I2121" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B2122" t="n">
-        <v>15780.7</v>
-      </c>
-      <c r="C2122" t="n">
-        <v>186502.7</v>
-      </c>
-      <c r="D2122" t="n">
-        <v>12615.8</v>
-      </c>
-      <c r="E2122" t="n">
-        <v>230022</v>
-      </c>
-      <c r="F2122" t="n">
-        <v>14576.7</v>
-      </c>
-      <c r="G2122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2122" t="n">
-        <v>459497.8</v>
-      </c>
-      <c r="I2122" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" s="4" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B2123" t="n">
-        <v>12414.3</v>
-      </c>
-      <c r="C2123" t="n">
-        <v>198767</v>
-      </c>
-      <c r="D2123" t="n">
-        <v>10182.2</v>
-      </c>
-      <c r="E2123" t="n">
-        <v>222054.3</v>
-      </c>
-      <c r="F2123" t="n">
-        <v>12766.8</v>
-      </c>
-      <c r="G2123" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2123" t="n">
-        <v>456184.7</v>
-      </c>
-      <c r="I2123" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" s="4" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B2124" t="n">
-        <v>10870.3</v>
-      </c>
-      <c r="C2124" t="n">
-        <v>176895.3</v>
-      </c>
-      <c r="D2124" t="n">
-        <v>8841.5</v>
-      </c>
-      <c r="E2124" t="n">
-        <v>232121.2</v>
-      </c>
-      <c r="F2124" t="n">
-        <v>673.5</v>
-      </c>
-      <c r="G2124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2124" t="n">
-        <v>429401.8</v>
-      </c>
-      <c r="I2124" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" s="4" t="n">
-        <v>46320</v>
-      </c>
-      <c r="B2125" t="n">
-        <v>8962.299999999999</v>
-      </c>
-      <c r="C2125" t="n">
-        <v>134550.2</v>
-      </c>
-      <c r="D2125" t="n">
-        <v>7060.7</v>
-      </c>
-      <c r="E2125" t="n">
-        <v>247471.7</v>
-      </c>
-      <c r="F2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2125" t="n">
-        <v>398044.8</v>
-      </c>
-      <c r="I2125" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" s="4" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B2126" t="n">
-        <v>11863.8</v>
-      </c>
-      <c r="C2126" t="n">
-        <v>146765.5</v>
-      </c>
-      <c r="D2126" t="n">
-        <v>9050.5</v>
-      </c>
-      <c r="E2126" t="n">
-        <v>258301.5</v>
-      </c>
-      <c r="F2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2126" t="n">
-        <v>425981.3</v>
-      </c>
-      <c r="I2126" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" s="4" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B2127" t="n">
-        <v>9068</v>
-      </c>
-      <c r="C2127" t="n">
-        <v>160672.3</v>
-      </c>
-      <c r="D2127" t="n">
-        <v>8783</v>
-      </c>
-      <c r="E2127" t="n">
-        <v>266823.3</v>
-      </c>
-      <c r="F2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2127" t="n">
-        <v>445346.7</v>
-      </c>
-      <c r="I2127" t="n">
         <v>144</v>
       </c>
     </row>
@@ -65451,7 +64699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2127"/>
+  <dimension ref="A1:D2102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94890,356 +94138,6 @@
         <v>16061</v>
       </c>
     </row>
-    <row r="2103">
-      <c r="A2103" s="4" t="n">
-        <v>46298</v>
-      </c>
-      <c r="B2103" t="n">
-        <v>17557</v>
-      </c>
-      <c r="C2103" t="n">
-        <v>20273</v>
-      </c>
-      <c r="D2103" t="n">
-        <v>15235</v>
-      </c>
-    </row>
-    <row r="2104">
-      <c r="A2104" s="4" t="n">
-        <v>46299</v>
-      </c>
-      <c r="B2104" t="n">
-        <v>16386</v>
-      </c>
-      <c r="C2104" t="n">
-        <v>19723</v>
-      </c>
-      <c r="D2104" t="n">
-        <v>14540</v>
-      </c>
-    </row>
-    <row r="2105">
-      <c r="A2105" s="4" t="n">
-        <v>46300</v>
-      </c>
-      <c r="B2105" t="n">
-        <v>18671</v>
-      </c>
-      <c r="C2105" t="n">
-        <v>21509</v>
-      </c>
-      <c r="D2105" t="n">
-        <v>15588</v>
-      </c>
-    </row>
-    <row r="2106">
-      <c r="A2106" s="4" t="n">
-        <v>46301</v>
-      </c>
-      <c r="B2106" t="n">
-        <v>19141</v>
-      </c>
-      <c r="C2106" t="n">
-        <v>21730</v>
-      </c>
-      <c r="D2106" t="n">
-        <v>16529</v>
-      </c>
-    </row>
-    <row r="2107">
-      <c r="A2107" s="4" t="n">
-        <v>46302</v>
-      </c>
-      <c r="B2107" t="n">
-        <v>19169</v>
-      </c>
-      <c r="C2107" t="n">
-        <v>21591</v>
-      </c>
-      <c r="D2107" t="n">
-        <v>16599</v>
-      </c>
-    </row>
-    <row r="2108">
-      <c r="A2108" s="4" t="n">
-        <v>46303</v>
-      </c>
-      <c r="B2108" t="n">
-        <v>19108</v>
-      </c>
-      <c r="C2108" t="n">
-        <v>21503</v>
-      </c>
-      <c r="D2108" t="n">
-        <v>16571</v>
-      </c>
-    </row>
-    <row r="2109">
-      <c r="A2109" s="4" t="n">
-        <v>46304</v>
-      </c>
-      <c r="B2109" t="n">
-        <v>19095</v>
-      </c>
-      <c r="C2109" t="n">
-        <v>21495</v>
-      </c>
-      <c r="D2109" t="n">
-        <v>16617</v>
-      </c>
-    </row>
-    <row r="2110">
-      <c r="A2110" s="4" t="n">
-        <v>46305</v>
-      </c>
-      <c r="B2110" t="n">
-        <v>18080</v>
-      </c>
-      <c r="C2110" t="n">
-        <v>20166</v>
-      </c>
-      <c r="D2110" t="n">
-        <v>15890</v>
-      </c>
-    </row>
-    <row r="2111">
-      <c r="A2111" s="4" t="n">
-        <v>46306</v>
-      </c>
-      <c r="B2111" t="n">
-        <v>16973</v>
-      </c>
-      <c r="C2111" t="n">
-        <v>19800</v>
-      </c>
-      <c r="D2111" t="n">
-        <v>14632</v>
-      </c>
-    </row>
-    <row r="2112">
-      <c r="A2112" s="4" t="n">
-        <v>46307</v>
-      </c>
-      <c r="B2112" t="n">
-        <v>18459</v>
-      </c>
-      <c r="C2112" t="n">
-        <v>20568</v>
-      </c>
-      <c r="D2112" t="n">
-        <v>15549</v>
-      </c>
-    </row>
-    <row r="2113">
-      <c r="A2113" s="4" t="n">
-        <v>46308</v>
-      </c>
-      <c r="B2113" t="n">
-        <v>18627</v>
-      </c>
-      <c r="C2113" t="n">
-        <v>21343</v>
-      </c>
-      <c r="D2113" t="n">
-        <v>15776</v>
-      </c>
-    </row>
-    <row r="2114">
-      <c r="A2114" s="4" t="n">
-        <v>46309</v>
-      </c>
-      <c r="B2114" t="n">
-        <v>19093</v>
-      </c>
-      <c r="C2114" t="n">
-        <v>21855</v>
-      </c>
-      <c r="D2114" t="n">
-        <v>16308</v>
-      </c>
-    </row>
-    <row r="2115">
-      <c r="A2115" s="4" t="n">
-        <v>46310</v>
-      </c>
-      <c r="B2115" t="n">
-        <v>19187</v>
-      </c>
-      <c r="C2115" t="n">
-        <v>21691</v>
-      </c>
-      <c r="D2115" t="n">
-        <v>16594</v>
-      </c>
-    </row>
-    <row r="2116">
-      <c r="A2116" s="4" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B2116" t="n">
-        <v>18822</v>
-      </c>
-      <c r="C2116" t="n">
-        <v>20994</v>
-      </c>
-      <c r="D2116" t="n">
-        <v>16479</v>
-      </c>
-    </row>
-    <row r="2117">
-      <c r="A2117" s="4" t="n">
-        <v>46312</v>
-      </c>
-      <c r="B2117" t="n">
-        <v>17872</v>
-      </c>
-      <c r="C2117" t="n">
-        <v>19972</v>
-      </c>
-      <c r="D2117" t="n">
-        <v>15590</v>
-      </c>
-    </row>
-    <row r="2118">
-      <c r="A2118" s="4" t="n">
-        <v>46313</v>
-      </c>
-      <c r="B2118" t="n">
-        <v>16801</v>
-      </c>
-      <c r="C2118" t="n">
-        <v>19535</v>
-      </c>
-      <c r="D2118" t="n">
-        <v>14801</v>
-      </c>
-    </row>
-    <row r="2119">
-      <c r="A2119" s="4" t="n">
-        <v>46314</v>
-      </c>
-      <c r="B2119" t="n">
-        <v>18184</v>
-      </c>
-      <c r="C2119" t="n">
-        <v>21873</v>
-      </c>
-      <c r="D2119" t="n">
-        <v>15309</v>
-      </c>
-    </row>
-    <row r="2120">
-      <c r="A2120" s="4" t="n">
-        <v>46315</v>
-      </c>
-      <c r="B2120" t="n">
-        <v>19220</v>
-      </c>
-      <c r="C2120" t="n">
-        <v>21481</v>
-      </c>
-      <c r="D2120" t="n">
-        <v>16723</v>
-      </c>
-    </row>
-    <row r="2121">
-      <c r="A2121" s="4" t="n">
-        <v>46316</v>
-      </c>
-      <c r="B2121" t="n">
-        <v>19024</v>
-      </c>
-      <c r="C2121" t="n">
-        <v>21591</v>
-      </c>
-      <c r="D2121" t="n">
-        <v>16328</v>
-      </c>
-    </row>
-    <row r="2122">
-      <c r="A2122" s="4" t="n">
-        <v>46317</v>
-      </c>
-      <c r="B2122" t="n">
-        <v>19166</v>
-      </c>
-      <c r="C2122" t="n">
-        <v>21833</v>
-      </c>
-      <c r="D2122" t="n">
-        <v>16483</v>
-      </c>
-    </row>
-    <row r="2123">
-      <c r="A2123" s="4" t="n">
-        <v>46318</v>
-      </c>
-      <c r="B2123" t="n">
-        <v>19027</v>
-      </c>
-      <c r="C2123" t="n">
-        <v>20955</v>
-      </c>
-      <c r="D2123" t="n">
-        <v>16774</v>
-      </c>
-    </row>
-    <row r="2124">
-      <c r="A2124" s="4" t="n">
-        <v>46319</v>
-      </c>
-      <c r="B2124" t="n">
-        <v>17910</v>
-      </c>
-      <c r="C2124" t="n">
-        <v>20306</v>
-      </c>
-      <c r="D2124" t="n">
-        <v>15828</v>
-      </c>
-    </row>
-    <row r="2125">
-      <c r="A2125" s="4" t="n">
-        <v>46320</v>
-      </c>
-      <c r="B2125" t="n">
-        <v>16576</v>
-      </c>
-      <c r="C2125" t="n">
-        <v>18892</v>
-      </c>
-      <c r="D2125" t="n">
-        <v>14760</v>
-      </c>
-    </row>
-    <row r="2126">
-      <c r="A2126" s="4" t="n">
-        <v>46321</v>
-      </c>
-      <c r="B2126" t="n">
-        <v>17732</v>
-      </c>
-      <c r="C2126" t="n">
-        <v>20754</v>
-      </c>
-      <c r="D2126" t="n">
-        <v>14911</v>
-      </c>
-    </row>
-    <row r="2127">
-      <c r="A2127" s="4" t="n">
-        <v>46322</v>
-      </c>
-      <c r="B2127" t="n">
-        <v>18525</v>
-      </c>
-      <c r="C2127" t="n">
-        <v>20616</v>
-      </c>
-      <c r="D2127" t="n">
-        <v>15865</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
